--- a/evaluation_forms/032_mentee_progress_check_in--evaluation_forms.xlsx
+++ b/evaluation_forms/032_mentee_progress_check_in--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is the mentee name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Mentee Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter mentee's name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>goal_1</t>
+          <t>mentee_progress_check_in_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Goal 1 title</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Goal 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select a goal for the mentee</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_2</t>
+          <t>mentee_progress_check_in_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Current Progress</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter current progress</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_3</t>
+          <t>mentee_progress_check_in_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Progress Date</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter progress date</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_4</t>
+          <t>mentee_progress_check_in_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Progress Time</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter progress time</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_5</t>
+          <t>mentee_progress_check_in_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Goal 1 Value</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate mentee's progress on Goal 1</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_6</t>
+          <t>mentee_progress_check_in_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Goal 2 Value</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rate mentee's progress on Goal 2</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -681,38 +709,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_7</t>
+          <t>mentee_progress_check_in_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Goal 3 Value</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rate mentee's progress on Goal 3</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_8</t>
+          <t>mentee_progress_check_in_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Progress Notes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Provide additional comments</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,43 +758,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_9</t>
+          <t>mentee_progress_check_in_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Goal 1 Progress Status</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select progress status for Goal 1</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_10</t>
+          <t>mentee_progress_check_in_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Goal 2 Progress Status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select progress status for Goal 2</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_11</t>
+          <t>mentee_progress_check_in_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Goal 3 Progress Status</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select progress status for Goal 3</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_12</t>
+          <t>mentee_progress_check_in_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Goal 1 Progress Details</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Provide progress details for Goal 1</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_13</t>
+          <t>mentee_progress_check_in_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Goal 2 Progress Details</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Provide progress details for Goal 2</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_14</t>
+          <t>mentee_progress_check_in_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Goal 3 Progress Details</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Provide progress details for Goal 3</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -860,43 +920,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_15</t>
+          <t>mentee_progress_check_in_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Progress Frequency</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Check in frequency</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_16</t>
+          <t>mentee_progress_check_in_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Mentee Feedback</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Provide feedback for the mentee</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,38 +979,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_17</t>
+          <t>mentee_progress_check_in_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Provide additional comments</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_18</t>
+          <t>mentee_progress_check_in_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Mentee Progress Check In 19</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Select a goal for the mentee</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>yes</t>
@@ -952,89 +1028,105 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_19</t>
+          <t>mentee_progress_check_in_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Goal 2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Select a goal for the mentee</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_20</t>
+          <t>mentee_progress_check_in_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Goal 3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Select a goal for the mentee</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_21</t>
+          <t>mentee_progress_check_in_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Mentee Progress Check In 22</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Select a goal for the mentee</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_22</t>
+          <t>mentee_progress_check_in_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Mentee Progress Check In 23</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Select a goal for the mentee</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1044,20 +1136,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_23</t>
+          <t>mentee_progress_check_in_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Progress Check In 2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Progress check in 2</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
@@ -1067,20 +1163,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_24</t>
+          <t>mentee_progress_check_in_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What is the mentee progress</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Progress Check In 3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Progress check in 3</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
@@ -1098,12 +1198,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +1226,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>goal_1_choices</t>
+          <t>mentee_progress_check_in_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>goal_1_choices</t>
+          <t>mentee_progress_check_in_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>goal_1_choices</t>
+          <t>mentee_progress_check_in_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1282,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1299,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1316,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1333,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1350,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1367,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1384,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1401,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1318,267 +1418,318 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_13_choices</t>
+          <t>mentee_progress_check_in_16_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_13_choices</t>
+          <t>mentee_progress_check_in_16_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_13_choices</t>
+          <t>mentee_progress_check_in_16_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_14_choices</t>
+          <t>mentee_progress_check_in_19_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_14_choices</t>
+          <t>mentee_progress_check_in_19_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_14_choices</t>
+          <t>mentee_progress_check_in_19_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_22_choices</t>
+          <t>mentee_progress_check_in_20_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_22_choices</t>
+          <t>mentee_progress_check_in_20_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_22_choices</t>
+          <t>mentee_progress_check_in_20_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_23_choices</t>
+          <t>mentee_progress_check_in_21_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_23_choices</t>
+          <t>mentee_progress_check_in_21_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_23_choices</t>
+          <t>mentee_progress_check_in_21_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_24_choices</t>
+          <t>mentee_progress_check_in_22_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'goal_1',_'value':_'goal_1'}</t>
+          <t>goal_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Goal 1', 'value': 'Goal 1'}</t>
+          <t>Goal 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_24_choices</t>
+          <t>mentee_progress_check_in_22_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'goal_2',_'value':_'goal_2'}</t>
+          <t>goal_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Goal 2', 'value': 'Goal 2'}</t>
+          <t>Goal 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mentee_progress_check_in_24_choices</t>
+          <t>mentee_progress_check_in_22_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'goal_3',_'value':_'goal_3'}</t>
+          <t>goal_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Goal 3', 'value': 'Goal 3'}</t>
+          <t>Goal 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mentee_progress_check_in_23_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>goal_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Goal 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mentee_progress_check_in_23_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>goal_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Goal 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mentee_progress_check_in_23_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>goal_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Goal 3</t>
         </is>
       </c>
     </row>
